--- a/output/pdf_financials_xlsx/OTEX.xlsx
+++ b/output/pdf_financials_xlsx/OTEX.xlsx
@@ -3360,49 +3360,49 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>29.678</v>
+        <v>231.018</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>45.613</v>
+        <v>231.129</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>43.464</v>
+        <v>246.646</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>42.809</v>
+        <v>387.845</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>53.191</v>
+        <v>358.473</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>59.021</v>
+        <v>376.677</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>81.625</v>
+        <v>560.12</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>101.059</v>
+        <v>644.638</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>97.238</v>
+        <v>620.319</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>136.436</v>
+        <v>693.549</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>98.551</v>
+        <v>594.754</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>120.552</v>
+        <v>591.626</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>221.732</v>
+        <v>1043.606</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>242.911</v>
+        <v>996.663</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>198.575</v>
+        <v>1044.962</v>
       </c>
     </row>
     <row r="49">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -25297,7 +25297,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">

--- a/output/pdf_financials_xlsx/OTEX.xlsx
+++ b/output/pdf_financials_xlsx/OTEX.xlsx
@@ -2175,49 +2175,49 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>129.13</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>159.485</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>186.851</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>186.177</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>240.147</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>242.368</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>345.715</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>456.929</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>470.928</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>514.734</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>520.605</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>503.953</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>657.351</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>807.925</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>641.244</v>
       </c>
     </row>
     <row r="29">
@@ -2237,49 +2237,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>136.134</v>
+        <v>265.264</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>137.345</v>
+        <v>296.83</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>178.21</v>
+        <v>365.061</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>276.535</v>
+        <v>462.712</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>266.044</v>
+        <v>506.191</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>290.777</v>
+        <v>533.145</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>249.551</v>
+        <v>595.266</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>386.126</v>
+        <v>843.0549999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>440.574</v>
+        <v>911.502</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>345.205</v>
+        <v>859.939</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>650.77</v>
+        <v>1171.375</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>516.011</v>
+        <v>1019.964</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>221.333</v>
+        <v>878.684</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>729.296</v>
+        <v>1537.221</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>482.071</v>
+        <v>1123.315</v>
       </c>
     </row>
     <row r="30">
@@ -2299,49 +2299,49 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>13.17464480408941</v>
+        <v>25.67146325908277</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>11.37458146062065</v>
+        <v>24.58274429324713</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.07161257386294</v>
+        <v>26.77703808892306</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>17.02069121726547</v>
+        <v>28.47985996175292</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>14.36587060867199</v>
+        <v>27.33335241266212</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>15.93972902509993</v>
+        <v>29.22578756602793</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.8923959552294</v>
+        <v>25.98215583462131</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>13.71555756682998</v>
+        <v>29.94610408132021</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>15.3576725792199</v>
+        <v>31.7734348175428</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>11.10078154544309</v>
+        <v>27.65311910721682</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>19.21878022453461</v>
+        <v>34.59347954809568</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>14.76914825046568</v>
+        <v>29.19317519614499</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.934982987661037</v>
+        <v>19.59170386490018</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.64037207580382</v>
+        <v>26.64356503085061</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9.327268277157073</v>
+        <v>21.73426811559852</v>
       </c>
     </row>
     <row r="31">
@@ -6552,52 +6552,52 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>113.837</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>129.13</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>159.485</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>186.851</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>186.177</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>240.147</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>242.368</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>345.715</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>456.929</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>470.928</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>514.734</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>520.605</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>503.953</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>657.351</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>807.925</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>641.244</v>
       </c>
     </row>
     <row r="101">
@@ -34310,7 +34310,11 @@
           <t>Depreciation and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -40421,7 +40425,11 @@
           <t>Depreciation and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OTEX.xlsx
+++ b/output/pdf_financials_xlsx/OTEX.xlsx
@@ -6732,52 +6732,52 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>1.833</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-2.079</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>4.242</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>11.146</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-3.534</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-7.766</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-7.274</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.819</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-6.897</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>37.733</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-13.954</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>-23.035</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>-28.395</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>42.486</v>
       </c>
     </row>
     <row r="104">
@@ -6912,52 +6912,52 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>16.258</v>
+        <v>15.444</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-10.259</v>
+        <v>-8.426</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-17.074</v>
+        <v>-19.153</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-18.564</v>
+        <v>-14.322</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-37.063</v>
+        <v>-25.917</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>27.25</v>
+        <v>23.716</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-1.467</v>
+        <v>-1.151</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-69.81</v>
+        <v>-77.57599999999999</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-78.587</v>
+        <v>-85.861</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>51.949</v>
+        <v>51.13</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>140.418</v>
+        <v>133.521</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>126.337</v>
+        <v>164.07</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>52.428</v>
+        <v>38.474</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-86.883</v>
+        <v>-109.918</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>-0.299</v>
+        <v>-28.694</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>60.65</v>
+        <v>103.136</v>
       </c>
     </row>
     <row r="107">
@@ -6972,52 +6972,52 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>9.765000000000001</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>11.308</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>18.097</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>15.575</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>19.906</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>22.047</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>25.978</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>30.507</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>27.594</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>26.77</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>29.532</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>51.969</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>69.556</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>130.302</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>140.079</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>104.84</v>
       </c>
     </row>
     <row r="108">
@@ -7845,19 +7845,19 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-119.105</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-176.987</v>
       </c>
       <c r="P121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-150.017</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-413.256</v>
       </c>
     </row>
     <row r="122">
@@ -8415,35 +8415,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M130" s="3" t="n">
+        <v>943.543</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>1697.263</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>1609.8</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>1695.911</v>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>1233.952</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>1282.793</v>
       </c>
     </row>
     <row r="131">
@@ -8548,22 +8536,22 @@
         <v>263.378</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>753.898</v>
+        <v>753.72</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>-117.197</v>
+        <v>-87.46299999999999</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>149.307</v>
+        <v>86.111</v>
       </c>
       <c r="P132" s="3" t="n">
-        <v>-469.162</v>
+        <v>-461.959</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>61.104</v>
+        <v>48.841</v>
       </c>
       <c r="R132" s="3" t="n">
-        <v>-157.569</v>
+        <v>-124.687</v>
       </c>
     </row>
     <row r="133">
@@ -8609,35 +8597,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M133" s="3" t="n">
+        <v>1697.263</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>1609.8</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>1695.911</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>1233.952</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>1282.793</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>1158.106</v>
       </c>
     </row>
     <row r="134">
@@ -34403,7 +34379,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35501,7 +35481,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -37132,7 +37116,11 @@
           <t>Repurchase of Common Shares</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37644,7 +37632,11 @@
           <t>Cash, cash equivalents and restricted cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37735,7 +37727,11 @@
           <t>Cash, cash equivalents and restricted cash at end of the year $</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -40510,7 +40506,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -41974,7 +41974,11 @@
           <t>Excess tax (benefits) expense on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -42677,7 +42681,11 @@
           <t>Excess tax benefits (expense) on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -43740,7 +43748,11 @@
           <t>Excess tax benefits on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45019,7 +45031,11 @@
           <t>Excess tax benefits on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -47813,7 +47829,11 @@
           <t>Excess tax benefits on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
